--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -554,7 +554,7 @@
         <v>30</v>
       </c>
       <c r="F2">
-        <v>47.86</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -568,13 +568,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>54.6</v>
+        <v>54.60009765625</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
       </c>
       <c r="F3">
-        <v>66.86</v>
+        <v>66.85986328125</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -588,13 +588,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>84.86</v>
+        <v>84.85986328125</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
       </c>
       <c r="F4">
-        <v>49.76</v>
+        <v>49.760009765625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -608,13 +608,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>47.86</v>
+        <v>47.860107421875</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5">
-        <v>72.7</v>
+        <v>72.7001953125</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -628,13 +628,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>60.16</v>
+        <v>60.159912109375</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
       </c>
       <c r="F6">
-        <v>72.86</v>
+        <v>72.85986328125</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -648,13 +648,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>74.06</v>
+        <v>74.06005859375</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
       </c>
       <c r="F7">
-        <v>61.56</v>
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -668,13 +668,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>73.95999999999999</v>
+        <v>73.9599609375</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
       </c>
       <c r="F8">
-        <v>53.66</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -688,13 +688,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>64.7</v>
+        <v>64.7001953125</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
       </c>
       <c r="F9">
-        <v>68.06</v>
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -708,13 +708,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>63.9</v>
+        <v>63.89990234375</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
       </c>
       <c r="F10">
-        <v>84.26000000000001</v>
+        <v>84.259765625</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -728,13 +728,13 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>54.16</v>
+        <v>54.159912109375</v>
       </c>
       <c r="E11" t="s">
         <v>39</v>
       </c>
       <c r="F11">
-        <v>72.45</v>
+        <v>72.4501953125</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -748,13 +748,13 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>38.26</v>
+        <v>38.260009765625</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12">
-        <v>62.56</v>
+        <v>62.56005859375</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -768,7 +768,7 @@
         <v>25</v>
       </c>
       <c r="D13">
-        <v>60.2</v>
+        <v>60.199951171875</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
@@ -788,13 +788,13 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>54.1</v>
+        <v>54.10009765625</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
       </c>
       <c r="F14">
-        <v>61.96</v>
+        <v>61.9599609375</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>73.76000000000001</v>
+        <v>73.759765625</v>
       </c>
       <c r="E15" t="s">
         <v>43</v>
       </c>
       <c r="F15">
-        <v>57.6</v>
+        <v>57.60009765625</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -828,13 +828,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>42.96</v>
+        <v>42.9599609375</v>
       </c>
       <c r="E16" t="s">
         <v>44</v>
       </c>
       <c r="F16">
-        <v>57.45</v>
+        <v>57.449951171875</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -848,13 +848,13 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>68.06</v>
+        <v>68.06005859375</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17">
-        <v>58.96</v>
+        <v>58.9599609375</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -897,9 +897,15 @@
       <c r="C2" t="s">
         <v>31</v>
       </c>
+      <c r="D2">
+        <v>50.35</v>
+      </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -911,8 +917,14 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
+      <c r="D3">
+        <v>52.8</v>
+      </c>
       <c r="E3" t="s">
         <v>15</v>
+      </c>
+      <c r="F3">
+        <v>69.2</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -925,8 +937,14 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
+      <c r="D4">
+        <v>15.7</v>
+      </c>
       <c r="E4" t="s">
         <v>16</v>
+      </c>
+      <c r="F4">
+        <v>45.15</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -939,8 +957,14 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
+      <c r="D5">
+        <v>38.7</v>
+      </c>
       <c r="E5" t="s">
         <v>17</v>
+      </c>
+      <c r="F5">
+        <v>49.4</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -953,8 +977,14 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
+      <c r="D6">
+        <v>41.7</v>
+      </c>
       <c r="E6" t="s">
         <v>18</v>
+      </c>
+      <c r="F6">
+        <v>26.1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -967,8 +997,14 @@
       <c r="C7" t="s">
         <v>34</v>
       </c>
+      <c r="D7">
+        <v>46.95</v>
+      </c>
       <c r="E7" t="s">
         <v>19</v>
+      </c>
+      <c r="F7">
+        <v>83.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -981,8 +1017,14 @@
       <c r="C8" t="s">
         <v>37</v>
       </c>
+      <c r="D8">
+        <v>58.3</v>
+      </c>
       <c r="E8" t="s">
         <v>20</v>
+      </c>
+      <c r="F8">
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -995,8 +1037,14 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
+      <c r="D9">
+        <v>49.8</v>
+      </c>
       <c r="E9" t="s">
         <v>21</v>
+      </c>
+      <c r="F9">
+        <v>35.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1009,8 +1057,14 @@
       <c r="C10" t="s">
         <v>39</v>
       </c>
+      <c r="D10">
+        <v>51.9</v>
+      </c>
       <c r="E10" t="s">
         <v>22</v>
+      </c>
+      <c r="F10">
+        <v>63.55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1023,8 +1077,14 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
+      <c r="D11">
+        <v>50.3</v>
+      </c>
       <c r="E11" t="s">
         <v>23</v>
+      </c>
+      <c r="F11">
+        <v>59.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1037,8 +1097,14 @@
       <c r="C12" t="s">
         <v>40</v>
       </c>
+      <c r="D12">
+        <v>55.9</v>
+      </c>
       <c r="E12" t="s">
         <v>25</v>
+      </c>
+      <c r="F12">
+        <v>45.9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1051,8 +1117,14 @@
       <c r="C13" t="s">
         <v>41</v>
       </c>
+      <c r="D13">
+        <v>37.8</v>
+      </c>
       <c r="E13" t="s">
         <v>24</v>
+      </c>
+      <c r="F13">
+        <v>66.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1065,8 +1137,14 @@
       <c r="C14" t="s">
         <v>43</v>
       </c>
+      <c r="D14">
+        <v>79.59999999999999</v>
+      </c>
       <c r="E14" t="s">
         <v>26</v>
+      </c>
+      <c r="F14">
+        <v>65.5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1079,8 +1157,14 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
+      <c r="D15">
+        <v>42.5</v>
+      </c>
       <c r="E15" t="s">
         <v>27</v>
+      </c>
+      <c r="F15">
+        <v>53.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1093,11 +1177,17 @@
       <c r="C16" t="s">
         <v>45</v>
       </c>
+      <c r="D16">
+        <v>38.8</v>
+      </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1107,8 +1197,14 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
+      <c r="D17">
+        <v>35.75</v>
+      </c>
       <c r="E17" t="s">
         <v>29</v>
+      </c>
+      <c r="F17">
+        <v>41.7</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -918,7 +918,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -964,7 +964,7 @@
         <v>17</v>
       </c>
       <c r="F5">
-        <v>49.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="6" spans="1:6">

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -898,13 +898,13 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>50.35</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -918,13 +918,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>69.2</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -938,13 +938,13 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>15.7</v>
+        <v>39.71</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>45.15</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -958,13 +958,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>38.7</v>
+        <v>55.81</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>52.8</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -978,13 +978,13 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6">
-        <v>26.1</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -998,13 +998,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>46.95</v>
+        <v>50.55</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>83.55</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1018,13 +1018,13 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8">
-        <v>65.40000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1038,13 +1038,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9">
-        <v>35.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1058,13 +1058,13 @@
         <v>39</v>
       </c>
       <c r="D10">
-        <v>51.9</v>
+        <v>61.01</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10">
-        <v>63.55</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1078,13 +1078,13 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>50.3</v>
+        <v>77.52</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
-        <v>59.95</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1098,13 +1098,13 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>45.9</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1118,13 +1118,13 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>37.8</v>
+        <v>53.11</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>66.55</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1144,7 +1144,7 @@
         <v>26</v>
       </c>
       <c r="F14">
-        <v>65.5</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1158,13 +1158,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>42.5</v>
+        <v>54.01</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
       </c>
       <c r="F15">
-        <v>53.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1178,13 +1178,13 @@
         <v>45</v>
       </c>
       <c r="D16">
-        <v>38.8</v>
+        <v>56.91</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16">
-        <v>62.4</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1198,13 +1198,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>35.75</v>
+        <v>49.15</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -898,13 +898,13 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>65.15000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>40.21</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -918,13 +918,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>73.70999999999999</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -938,13 +938,13 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>39.71</v>
+        <v>64.58</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>61.95</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -958,13 +958,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>55.81</v>
+        <v>77.48</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>61.91</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -978,13 +978,13 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6">
-        <v>48.01</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -998,13 +998,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>50.55</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>88.36</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1018,13 +1018,13 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>59.2</v>
+        <v>72.56</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8">
-        <v>69.7</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1038,13 +1038,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9">
-        <v>48</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1058,13 +1058,13 @@
         <v>39</v>
       </c>
       <c r="D10">
-        <v>61.01</v>
+        <v>88.98</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10">
-        <v>75.16</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1078,13 +1078,13 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>77.52</v>
+        <v>82.61</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
-        <v>63.95</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1098,13 +1098,13 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>66.11</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1118,13 +1118,13 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>53.11</v>
+        <v>73.78</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>78.84999999999999</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1138,13 +1138,13 @@
         <v>43</v>
       </c>
       <c r="D14">
-        <v>79.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
       </c>
       <c r="F14">
-        <v>66.40000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1158,13 +1158,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>54.01</v>
+        <v>84.48</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
       </c>
       <c r="F15">
-        <v>58.2</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1178,13 +1178,13 @@
         <v>45</v>
       </c>
       <c r="D16">
-        <v>56.91</v>
+        <v>79.28</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16">
-        <v>71.51000000000001</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1198,13 +1198,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>49.15</v>
+        <v>83.2</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -898,13 +898,13 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>92.7</v>
+        <v>92.7001953125</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>36.43</v>
+        <v>36.429931640625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -918,13 +918,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>72.18000000000001</v>
+        <v>72.18017578125</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>85.58</v>
+        <v>85.580078125</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -938,13 +938,13 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>64.58</v>
+        <v>64.580078125</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>79.45</v>
+        <v>79.4501953125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -958,13 +958,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>77.48</v>
+        <v>77.47998046875</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>81.88</v>
+        <v>81.8798828125</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -978,13 +978,13 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6">
-        <v>64.58</v>
+        <v>64.580078125</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -998,13 +998,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>93.78</v>
+        <v>93.77978515625</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1018,13 +1018,13 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>72.56</v>
+        <v>72.7001953125</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8">
-        <v>92.76000000000001</v>
+        <v>92.89990234375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1038,13 +1038,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>81.48</v>
+        <v>81.47998046875</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9">
-        <v>60.7</v>
+        <v>60.699951171875</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1058,13 +1058,13 @@
         <v>39</v>
       </c>
       <c r="D10">
-        <v>88.98</v>
+        <v>88.97998046875</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10">
-        <v>92.78</v>
+        <v>92.77978515625</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1078,13 +1078,13 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>82.61</v>
+        <v>82.60986328125</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
-        <v>86.7</v>
+        <v>86.7001953125</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1098,13 +1098,13 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>96.48</v>
+        <v>96.47998046875</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>92.33</v>
+        <v>92.330078125</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1118,7 +1118,7 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>73.78</v>
+        <v>73.77978515625</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
@@ -1158,13 +1158,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>84.48</v>
+        <v>84.47998046875</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
       </c>
       <c r="F15">
-        <v>81.26000000000001</v>
+        <v>81.39990234375</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1178,13 +1178,13 @@
         <v>45</v>
       </c>
       <c r="D16">
-        <v>79.28</v>
+        <v>79.27978515625</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16">
-        <v>91.48</v>
+        <v>91.47998046875</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1198,13 +1198,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>83.2</v>
+        <v>83.2001953125</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1247,9 +1247,15 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2">
+        <v>17.5</v>
+      </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -1261,8 +1267,14 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
+      <c r="D3">
+        <v>62.8</v>
+      </c>
       <c r="E3" t="s">
         <v>31</v>
+      </c>
+      <c r="F3">
+        <v>55.19</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1275,8 +1287,14 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4">
+        <v>21.6</v>
+      </c>
       <c r="E4" t="s">
         <v>17</v>
+      </c>
+      <c r="F4">
+        <v>69.27</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1289,8 +1307,14 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
+      <c r="D5">
+        <v>70.37</v>
+      </c>
       <c r="E5" t="s">
         <v>33</v>
+      </c>
+      <c r="F5">
+        <v>58.4</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1303,8 +1327,14 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
+      <c r="D6">
+        <v>57.47</v>
+      </c>
       <c r="E6" t="s">
         <v>19</v>
+      </c>
+      <c r="F6">
+        <v>54.97</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1317,8 +1347,14 @@
       <c r="C7" t="s">
         <v>34</v>
       </c>
+      <c r="D7">
+        <v>42.46</v>
+      </c>
       <c r="E7" t="s">
         <v>35</v>
+      </c>
+      <c r="F7">
+        <v>45.17</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1331,8 +1367,14 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
+      <c r="D8">
+        <v>47.57</v>
+      </c>
       <c r="E8" t="s">
         <v>21</v>
+      </c>
+      <c r="F8">
+        <v>40.17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1345,8 +1387,14 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
+      <c r="D9">
+        <v>38.07</v>
+      </c>
       <c r="E9" t="s">
         <v>37</v>
+      </c>
+      <c r="F9">
+        <v>38.07</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1359,8 +1407,14 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
+      <c r="D10">
+        <v>40.6</v>
+      </c>
       <c r="E10" t="s">
         <v>23</v>
+      </c>
+      <c r="F10">
+        <v>59.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1373,8 +1427,14 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
+      <c r="D11">
+        <v>29.2</v>
+      </c>
       <c r="E11" t="s">
         <v>39</v>
+      </c>
+      <c r="F11">
+        <v>57.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1387,8 +1447,14 @@
       <c r="C12" t="s">
         <v>40</v>
       </c>
+      <c r="D12">
+        <v>53.77</v>
+      </c>
       <c r="E12" t="s">
         <v>41</v>
+      </c>
+      <c r="F12">
+        <v>54.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1401,8 +1467,14 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
+      <c r="D13">
+        <v>67.27</v>
+      </c>
       <c r="E13" t="s">
         <v>25</v>
+      </c>
+      <c r="F13">
+        <v>38.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1415,8 +1487,14 @@
       <c r="C14" t="s">
         <v>26</v>
       </c>
+      <c r="D14">
+        <v>50.77</v>
+      </c>
       <c r="E14" t="s">
         <v>27</v>
+      </c>
+      <c r="F14">
+        <v>40.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1429,8 +1507,14 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
+      <c r="D15">
+        <v>35.5</v>
+      </c>
       <c r="E15" t="s">
         <v>43</v>
+      </c>
+      <c r="F15">
+        <v>39.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1443,11 +1527,17 @@
       <c r="C16" t="s">
         <v>28</v>
       </c>
+      <c r="D16">
+        <v>58.47</v>
+      </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>45.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1457,8 +1547,14 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
+      <c r="D17">
+        <v>27.9</v>
+      </c>
       <c r="E17" t="s">
         <v>45</v>
+      </c>
+      <c r="F17">
+        <v>45.77</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1248,13 +1248,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>17.5</v>
+        <v>53.15</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2">
-        <v>58.37</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1268,13 +1268,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
       </c>
       <c r="F3">
-        <v>55.19</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1288,13 +1288,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>21.6</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4">
-        <v>69.27</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1308,13 +1308,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>70.37</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5">
-        <v>58.4</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1328,13 +1328,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>57.47</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6">
-        <v>54.97</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1348,13 +1348,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>42.46</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
       </c>
       <c r="F7">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1368,13 +1368,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>47.57</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
       </c>
       <c r="F8">
-        <v>40.17</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1388,13 +1388,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
       </c>
       <c r="F9">
-        <v>38.07</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1408,13 +1408,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>40.6</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10">
-        <v>59.87</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1428,13 +1428,13 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>29.2</v>
+        <v>81.25</v>
       </c>
       <c r="E11" t="s">
         <v>39</v>
       </c>
       <c r="F11">
-        <v>57.17</v>
+        <v>83.45999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1448,13 +1448,13 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="E12" t="s">
         <v>41</v>
       </c>
       <c r="F12">
-        <v>54.27</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1468,13 +1468,13 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>67.27</v>
+        <v>71.06</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
       </c>
       <c r="F13">
-        <v>38.27</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1488,13 +1488,13 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>50.77</v>
+        <v>72.16</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
       </c>
       <c r="F14">
-        <v>40.57</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1508,13 +1508,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>35.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E15" t="s">
         <v>43</v>
       </c>
       <c r="F15">
-        <v>39.87</v>
+        <v>78.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>58.47</v>
+        <v>98.56</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="F16">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1548,13 +1548,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>27.9</v>
+        <v>70.8</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17">
-        <v>45.77</v>
+        <v>86.66</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1248,13 +1248,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>53.15</v>
+        <v>54.35009765625</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2">
-        <v>66.95999999999999</v>
+        <v>67.759765625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1268,13 +1268,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>97.40000000000001</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
       </c>
       <c r="F3">
-        <v>73.23999999999999</v>
+        <v>72.740234375</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1288,13 +1288,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>78.26000000000001</v>
+        <v>78.93994140625</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4">
-        <v>97.76000000000001</v>
+        <v>97.759765625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1308,13 +1308,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>80.45999999999999</v>
+        <v>81.259765625</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5">
-        <v>98.65000000000001</v>
+        <v>98.64990234375</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1328,13 +1328,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>88.76000000000001</v>
+        <v>88.759765625</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6">
-        <v>93.45999999999999</v>
+        <v>94.259765625</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1348,13 +1348,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>80.70999999999999</v>
+        <v>80.2998046875</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
       </c>
       <c r="F7">
-        <v>105.76</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1368,13 +1368,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>81.76000000000001</v>
+        <v>81.759765625</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
       </c>
       <c r="F8">
-        <v>86.16</v>
+        <v>86.16015625</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1388,13 +1388,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>78.45999999999999</v>
+        <v>79.259765625</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
       </c>
       <c r="F9">
-        <v>79.06</v>
+        <v>79.85986328125</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1408,13 +1408,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>78.40000000000001</v>
+        <v>78.39990234375</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10">
-        <v>74.76000000000001</v>
+        <v>75.56005859375</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1434,7 +1434,7 @@
         <v>39</v>
       </c>
       <c r="F11">
-        <v>83.45999999999999</v>
+        <v>84.259765625</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1448,13 +1448,13 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>87.45999999999999</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E12" t="s">
         <v>41</v>
       </c>
       <c r="F12">
-        <v>92.95999999999999</v>
+        <v>93.759765625</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1468,13 +1468,13 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>71.06</v>
+        <v>71.85986328125</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
       </c>
       <c r="F13">
-        <v>79.76000000000001</v>
+        <v>80.56005859375</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1488,13 +1488,13 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>72.16</v>
+        <v>72.9599609375</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
       </c>
       <c r="F14">
-        <v>80.56</v>
+        <v>81.35986328125</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1508,13 +1508,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>87.40000000000001</v>
+        <v>87.39990234375</v>
       </c>
       <c r="E15" t="s">
         <v>43</v>
       </c>
       <c r="F15">
-        <v>78.86</v>
+        <v>78.85986328125</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>98.56</v>
+        <v>99.35986328125</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="F16">
-        <v>105.76</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1548,13 +1548,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>70.8</v>
+        <v>70.7998046875</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17">
-        <v>86.66</v>
+        <v>86.66015625</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1597,9 +1597,15 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2">
+        <v>21.65</v>
+      </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
+      <c r="F2">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -1611,8 +1617,14 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
+      <c r="D3">
+        <v>35.7</v>
+      </c>
       <c r="E3" t="s">
         <v>30</v>
+      </c>
+      <c r="F3">
+        <v>65.55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1625,8 +1637,14 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4">
+        <v>31.78</v>
+      </c>
       <c r="E4" t="s">
         <v>33</v>
+      </c>
+      <c r="F4">
+        <v>42.3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1639,8 +1657,14 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
+      <c r="D5">
+        <v>65.55</v>
+      </c>
       <c r="E5" t="s">
         <v>32</v>
+      </c>
+      <c r="F5">
+        <v>47.98</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1653,8 +1677,14 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
+      <c r="D6">
+        <v>58.2</v>
+      </c>
       <c r="E6" t="s">
         <v>35</v>
+      </c>
+      <c r="F6">
+        <v>43.8</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1667,8 +1697,14 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
+      <c r="D7">
+        <v>46.55</v>
+      </c>
       <c r="E7" t="s">
         <v>34</v>
+      </c>
+      <c r="F7">
+        <v>56.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1681,8 +1717,14 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
+      <c r="D8">
+        <v>25.3</v>
+      </c>
       <c r="E8" t="s">
         <v>37</v>
+      </c>
+      <c r="F8">
+        <v>32.73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1695,8 +1737,14 @@
       <c r="C9" t="s">
         <v>21</v>
       </c>
+      <c r="D9">
+        <v>47.45</v>
+      </c>
       <c r="E9" t="s">
         <v>36</v>
+      </c>
+      <c r="F9">
+        <v>59.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1709,8 +1757,14 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
+      <c r="D10">
+        <v>51.7</v>
+      </c>
       <c r="E10" t="s">
         <v>39</v>
+      </c>
+      <c r="F10">
+        <v>48.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1723,8 +1777,14 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
+      <c r="D11">
+        <v>34.9</v>
+      </c>
       <c r="E11" t="s">
         <v>38</v>
+      </c>
+      <c r="F11">
+        <v>18.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1737,8 +1797,14 @@
       <c r="C12" t="s">
         <v>25</v>
       </c>
+      <c r="D12">
+        <v>37.1</v>
+      </c>
       <c r="E12" t="s">
         <v>40</v>
+      </c>
+      <c r="F12">
+        <v>44.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1751,8 +1817,14 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
+      <c r="D13">
+        <v>38.75</v>
+      </c>
       <c r="E13" t="s">
         <v>41</v>
+      </c>
+      <c r="F13">
+        <v>44.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1765,8 +1837,14 @@
       <c r="C14" t="s">
         <v>26</v>
       </c>
+      <c r="D14">
+        <v>33.5</v>
+      </c>
       <c r="E14" t="s">
         <v>43</v>
+      </c>
+      <c r="F14">
+        <v>73.83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,8 +1857,14 @@
       <c r="C15" t="s">
         <v>27</v>
       </c>
+      <c r="D15">
+        <v>41.5</v>
+      </c>
       <c r="E15" t="s">
         <v>42</v>
+      </c>
+      <c r="F15">
+        <v>45.35</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1793,11 +1877,17 @@
       <c r="C16" t="s">
         <v>28</v>
       </c>
+      <c r="D16">
+        <v>41.55</v>
+      </c>
       <c r="E16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1807,8 +1897,14 @@
       <c r="C17" t="s">
         <v>29</v>
       </c>
+      <c r="D17">
+        <v>43.8</v>
+      </c>
       <c r="E17" t="s">
         <v>44</v>
+      </c>
+      <c r="F17">
+        <v>51.19</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>21.65</v>
+        <v>24.25</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2">
-        <v>48.89</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1618,13 +1618,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>35.7</v>
+        <v>40.05</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
       </c>
       <c r="F3">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1638,13 +1638,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>31.78</v>
+        <v>44.63</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
       <c r="F4">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1658,13 +1658,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>47.98</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1678,13 +1678,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>58.2</v>
+        <v>92.05</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
       <c r="F6">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1698,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>46.55</v>
+        <v>55.75</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7">
-        <v>56.4</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1718,13 +1718,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>25.3</v>
+        <v>31.15</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8">
-        <v>32.73</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1738,13 +1738,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>47.45</v>
+        <v>61.96</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
       </c>
       <c r="F9">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1758,13 +1758,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
       <c r="E10" t="s">
         <v>39</v>
       </c>
       <c r="F10">
-        <v>48.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1778,13 +1778,13 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>34.9</v>
+        <v>62.15</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
       <c r="F11">
-        <v>18.4</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1798,13 +1798,13 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>37.1</v>
+        <v>47.25</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1818,13 +1818,13 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>38.75</v>
+        <v>42.95</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
       </c>
       <c r="F13">
-        <v>44.07</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1838,13 +1838,13 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>33.5</v>
+        <v>33.95</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
       </c>
       <c r="F14">
-        <v>73.83</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>41.5</v>
+        <v>45.85</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
       </c>
       <c r="F15">
-        <v>45.35</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1878,13 +1878,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>41.55</v>
+        <v>45.75</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
       </c>
       <c r="F16">
-        <v>70.40000000000001</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1898,13 +1898,13 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
       <c r="E17" t="s">
         <v>44</v>
       </c>
       <c r="F17">
-        <v>51.19</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>24.25</v>
+        <v>29.85</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2">
-        <v>45.94</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1618,7 +1618,7 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>40.05</v>
+        <v>52.25</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -1638,13 +1638,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>44.63</v>
+        <v>47.73</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
       <c r="F4">
-        <v>38.5</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1664,7 +1664,7 @@
         <v>32</v>
       </c>
       <c r="F5">
-        <v>47.68</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1678,13 +1678,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>92.05</v>
+        <v>109.75</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
       <c r="F6">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1698,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>55.75</v>
+        <v>74.95</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7">
-        <v>67.05</v>
+        <v>77.05</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1718,13 +1718,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>31.15</v>
+        <v>53.25</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8">
-        <v>37.08</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1738,13 +1738,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>61.96</v>
+        <v>61.26</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
       </c>
       <c r="F9">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1758,13 +1758,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>64.05</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="E10" t="s">
         <v>39</v>
       </c>
       <c r="F10">
-        <v>51.5</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1778,13 +1778,13 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>62.15</v>
+        <v>82.05</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
       <c r="F11">
-        <v>22.15</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1798,13 +1798,13 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>47.25</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1818,13 +1818,13 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>42.95</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
       </c>
       <c r="F13">
-        <v>47.58</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1838,7 +1838,7 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>33.95</v>
+        <v>57.25</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -1858,7 +1858,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>45.85</v>
+        <v>65.05</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -1878,13 +1878,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>45.75</v>
+        <v>74.55</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
       </c>
       <c r="F16">
-        <v>78.66</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1898,13 +1898,13 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E17" t="s">
         <v>44</v>
       </c>
       <c r="F17">
-        <v>67.26000000000001</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>29.85</v>
+        <v>29.8499755859375</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2">
-        <v>50.59</v>
+        <v>50.590087890625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1624,7 +1624,7 @@
         <v>30</v>
       </c>
       <c r="F3">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1638,13 +1638,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>47.73</v>
+        <v>47.72998046875</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
       <c r="F4">
-        <v>85.48</v>
+        <v>85.47998046875</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1658,13 +1658,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>84.88</v>
+        <v>84.8798828125</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1684,7 +1684,7 @@
         <v>35</v>
       </c>
       <c r="F6">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1698,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>74.95</v>
+        <v>74.9501953125</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7">
-        <v>77.05</v>
+        <v>77.0498046875</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1724,7 +1724,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>58.68</v>
+        <v>58.679931640625</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1738,13 +1738,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>61.26</v>
+        <v>61.260009765625</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
       </c>
       <c r="F9">
-        <v>86.43000000000001</v>
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1758,13 +1758,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>87.65000000000001</v>
+        <v>87.64990234375</v>
       </c>
       <c r="E10" t="s">
         <v>39</v>
       </c>
       <c r="F10">
-        <v>70.7</v>
+        <v>70.7001953125</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1778,13 +1778,13 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>82.05</v>
+        <v>82.0498046875</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
       <c r="F11">
-        <v>45.65</v>
+        <v>45.64990234375</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1798,13 +1798,13 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>66.65000000000001</v>
+        <v>66.64990234375</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12">
-        <v>81.43000000000001</v>
+        <v>81.43017578125</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1818,13 +1818,13 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>83.15000000000001</v>
+        <v>83.14990234375</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
       </c>
       <c r="F13">
-        <v>51.93</v>
+        <v>51.929931640625</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1844,7 +1844,7 @@
         <v>43</v>
       </c>
       <c r="F14">
-        <v>85.98</v>
+        <v>85.97998046875</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>65.05</v>
+        <v>65.0498046875</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
       </c>
       <c r="F15">
-        <v>53.15</v>
+        <v>53.14990234375</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1878,13 +1878,13 @@
         <v>28</v>
       </c>
       <c r="D16">
-        <v>74.55</v>
+        <v>74.5498046875</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
       </c>
       <c r="F16">
-        <v>80.36</v>
+        <v>80.35986328125</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1898,13 +1898,13 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
       <c r="E17" t="s">
         <v>44</v>
       </c>
       <c r="F17">
-        <v>77.26000000000001</v>
+        <v>77.259765625</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1947,9 +1947,15 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
+      <c r="D2">
+        <v>6.1</v>
+      </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
+      <c r="F2">
+        <v>18.15</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -1961,8 +1967,14 @@
       <c r="C3" t="s">
         <v>31</v>
       </c>
+      <c r="D3">
+        <v>20.7</v>
+      </c>
       <c r="E3" t="s">
         <v>30</v>
+      </c>
+      <c r="F3">
+        <v>13.8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1975,8 +1987,14 @@
       <c r="C4" t="s">
         <v>17</v>
       </c>
+      <c r="D4">
+        <v>9.300000000000001</v>
+      </c>
       <c r="E4" t="s">
         <v>16</v>
+      </c>
+      <c r="F4">
+        <v>11.3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1989,8 +2007,14 @@
       <c r="C5" t="s">
         <v>33</v>
       </c>
+      <c r="D5">
+        <v>13.9</v>
+      </c>
       <c r="E5" t="s">
         <v>32</v>
+      </c>
+      <c r="F5">
+        <v>14.3</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2003,8 +2027,14 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
+      <c r="D6">
+        <v>41.6</v>
+      </c>
       <c r="E6" t="s">
         <v>18</v>
+      </c>
+      <c r="F6">
+        <v>20.6</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2017,8 +2047,14 @@
       <c r="C7" t="s">
         <v>35</v>
       </c>
+      <c r="D7">
+        <v>22.3</v>
+      </c>
       <c r="E7" t="s">
         <v>34</v>
+      </c>
+      <c r="F7">
+        <v>7.7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2031,8 +2067,14 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
       <c r="E8" t="s">
         <v>20</v>
+      </c>
+      <c r="F8">
+        <v>20.9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2045,8 +2087,14 @@
       <c r="C9" t="s">
         <v>37</v>
       </c>
+      <c r="D9">
+        <v>15.5</v>
+      </c>
       <c r="E9" t="s">
         <v>36</v>
+      </c>
+      <c r="F9">
+        <v>25.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2059,8 +2107,14 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
+      <c r="D10">
+        <v>9.300000000000001</v>
+      </c>
       <c r="E10" t="s">
         <v>22</v>
+      </c>
+      <c r="F10">
+        <v>10.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2073,8 +2127,14 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
+      <c r="D11">
+        <v>50.5</v>
+      </c>
       <c r="E11" t="s">
         <v>38</v>
+      </c>
+      <c r="F11">
+        <v>14.9</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2087,8 +2147,14 @@
       <c r="C12" t="s">
         <v>41</v>
       </c>
+      <c r="D12">
+        <v>22.2</v>
+      </c>
       <c r="E12" t="s">
         <v>40</v>
+      </c>
+      <c r="F12">
+        <v>11.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2101,8 +2167,14 @@
       <c r="C13" t="s">
         <v>25</v>
       </c>
+      <c r="D13">
+        <v>20.4</v>
+      </c>
       <c r="E13" t="s">
         <v>24</v>
+      </c>
+      <c r="F13">
+        <v>14.3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2115,8 +2187,14 @@
       <c r="C14" t="s">
         <v>27</v>
       </c>
+      <c r="D14">
+        <v>10.5</v>
+      </c>
       <c r="E14" t="s">
         <v>26</v>
+      </c>
+      <c r="F14">
+        <v>4.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2129,8 +2207,14 @@
       <c r="C15" t="s">
         <v>43</v>
       </c>
+      <c r="D15">
+        <v>27.1</v>
+      </c>
       <c r="E15" t="s">
         <v>42</v>
+      </c>
+      <c r="F15">
+        <v>47.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2143,11 +2227,17 @@
       <c r="C16" t="s">
         <v>29</v>
       </c>
+      <c r="D16">
+        <v>22.3</v>
+      </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2157,8 +2247,14 @@
       <c r="C17" t="s">
         <v>45</v>
       </c>
+      <c r="D17">
+        <v>11.3</v>
+      </c>
       <c r="E17" t="s">
         <v>44</v>
+      </c>
+      <c r="F17">
+        <v>20.17</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -1948,13 +1948,13 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>6.1</v>
+        <v>82.919921875</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>18.15</v>
+        <v>83.41015625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1968,13 +1968,13 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>20.7</v>
+        <v>81.169921875</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
       </c>
       <c r="F3">
-        <v>13.8</v>
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1988,13 +1988,13 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>9.300000000000001</v>
+        <v>74.31982421875</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>11.3</v>
+        <v>70.60009765625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2008,13 +2008,13 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>13.9</v>
+        <v>84.60986328125</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>14.3</v>
+        <v>77.47021484375</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2028,13 +2028,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>41.6</v>
+        <v>103.919921875</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="F6">
-        <v>20.6</v>
+        <v>81.47021484375</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2048,13 +2048,13 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>22.3</v>
+        <v>93.02001953125</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7">
-        <v>7.7</v>
+        <v>82.6201171875</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>90.3701171875</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8">
-        <v>20.9</v>
+        <v>83.31982421875</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2088,13 +2088,13 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>15.5</v>
+        <v>94.6201171875</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
       </c>
       <c r="F9">
-        <v>25.7</v>
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2108,13 +2108,13 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>9.300000000000001</v>
+        <v>77.919921875</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10">
-        <v>10.5</v>
+        <v>89.02001953125</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2128,13 +2128,13 @@
         <v>39</v>
       </c>
       <c r="D11">
-        <v>50.5</v>
+        <v>103.56982421875</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
       <c r="F11">
-        <v>14.9</v>
+        <v>72.27001953125</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2148,13 +2148,13 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>22.2</v>
+        <v>74.77001953125</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12">
-        <v>11.7</v>
+        <v>85.669921875</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2168,13 +2168,13 @@
         <v>25</v>
       </c>
       <c r="D13">
-        <v>20.4</v>
+        <v>69.10986328125</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>14.3</v>
+        <v>77.47021484375</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2188,13 +2188,13 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>10.5</v>
+        <v>95.6201171875</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
       </c>
       <c r="F14">
-        <v>4.2</v>
+        <v>79.52001953125</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>43</v>
       </c>
       <c r="D15">
-        <v>27.1</v>
+        <v>87.22021484375</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
       </c>
       <c r="F15">
-        <v>47.8</v>
+        <v>87.52001953125</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2228,13 +2228,13 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>22.3</v>
+        <v>93.02001953125</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16">
-        <v>18.7</v>
+        <v>96.1201171875</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2248,13 +2248,13 @@
         <v>45</v>
       </c>
       <c r="D17">
-        <v>11.3</v>
+        <v>98.52001953125</v>
       </c>
       <c r="E17" t="s">
         <v>44</v>
       </c>
       <c r="F17">
-        <v>20.17</v>
+        <v>69.3701171875</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -2297,9 +2297,15 @@
       <c r="C2" t="s">
         <v>31</v>
       </c>
+      <c r="D2">
+        <v>62.92</v>
+      </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2">
+        <v>54.21</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -2311,8 +2317,14 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
+      <c r="D3">
+        <v>62.01</v>
+      </c>
       <c r="E3" t="s">
         <v>14</v>
+      </c>
+      <c r="F3">
+        <v>48.2</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2325,8 +2337,14 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
+      <c r="D4">
+        <v>72.11</v>
+      </c>
       <c r="E4" t="s">
         <v>17</v>
+      </c>
+      <c r="F4">
+        <v>64.36</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2339,8 +2357,14 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
+      <c r="D5">
+        <v>64.12</v>
+      </c>
       <c r="E5" t="s">
         <v>16</v>
+      </c>
+      <c r="F5">
+        <v>44.51</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2353,8 +2377,14 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
+      <c r="D6">
+        <v>83</v>
+      </c>
       <c r="E6" t="s">
         <v>19</v>
+      </c>
+      <c r="F6">
+        <v>86.42</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2367,8 +2397,14 @@
       <c r="C7" t="s">
         <v>34</v>
       </c>
+      <c r="D7">
+        <v>66.61</v>
+      </c>
       <c r="E7" t="s">
         <v>18</v>
+      </c>
+      <c r="F7">
+        <v>56.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2381,8 +2417,14 @@
       <c r="C8" t="s">
         <v>37</v>
       </c>
+      <c r="D8">
+        <v>68.8</v>
+      </c>
       <c r="E8" t="s">
         <v>21</v>
+      </c>
+      <c r="F8">
+        <v>72.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2395,8 +2437,14 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
+      <c r="D9">
+        <v>47.39</v>
+      </c>
       <c r="E9" t="s">
         <v>20</v>
+      </c>
+      <c r="F9">
+        <v>54.81</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2409,8 +2457,14 @@
       <c r="C10" t="s">
         <v>39</v>
       </c>
+      <c r="D10">
+        <v>65.89</v>
+      </c>
       <c r="E10" t="s">
         <v>23</v>
+      </c>
+      <c r="F10">
+        <v>73.22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2423,8 +2477,14 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
+      <c r="D11">
+        <v>53.46</v>
+      </c>
       <c r="E11" t="s">
         <v>22</v>
+      </c>
+      <c r="F11">
+        <v>62.81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2437,8 +2497,14 @@
       <c r="C12" t="s">
         <v>41</v>
       </c>
+      <c r="D12">
+        <v>66.51000000000001</v>
+      </c>
       <c r="E12" t="s">
         <v>25</v>
+      </c>
+      <c r="F12">
+        <v>67.19</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2451,8 +2517,14 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
+      <c r="D13">
+        <v>58.61</v>
+      </c>
       <c r="E13" t="s">
         <v>24</v>
+      </c>
+      <c r="F13">
+        <v>54.62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2465,8 +2537,14 @@
       <c r="C14" t="s">
         <v>43</v>
       </c>
+      <c r="D14">
+        <v>62.1</v>
+      </c>
       <c r="E14" t="s">
         <v>27</v>
+      </c>
+      <c r="F14">
+        <v>69.42</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2479,8 +2557,14 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
+      <c r="D15">
+        <v>69.12</v>
+      </c>
       <c r="E15" t="s">
         <v>26</v>
+      </c>
+      <c r="F15">
+        <v>56.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2493,11 +2577,17 @@
       <c r="C16" t="s">
         <v>45</v>
       </c>
+      <c r="D16">
+        <v>77.41</v>
+      </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2507,8 +2597,14 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
+      <c r="D17">
+        <v>52.2</v>
+      </c>
       <c r="E17" t="s">
         <v>28</v>
+      </c>
+      <c r="F17">
+        <v>65.70999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -2298,13 +2298,13 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>62.92</v>
+        <v>62.919921875</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2">
-        <v>54.21</v>
+        <v>54.2099609375</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2318,13 +2318,13 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>62.01</v>
+        <v>62.010009765625</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3">
-        <v>48.2</v>
+        <v>48.199951171875</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2338,13 +2338,13 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>72.11</v>
+        <v>72.10986328125</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4">
-        <v>64.36</v>
+        <v>64.35986328125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2358,13 +2358,13 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>64.12</v>
+        <v>64.1201171875</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5">
-        <v>44.51</v>
+        <v>44.510009765625</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2384,7 +2384,7 @@
         <v>19</v>
       </c>
       <c r="F6">
-        <v>86.42</v>
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2398,13 +2398,13 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>66.61</v>
+        <v>66.60986328125</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
       <c r="F7">
-        <v>56.4</v>
+        <v>56.39990234375</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2418,13 +2418,13 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>68.8</v>
+        <v>68.7998046875</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
       </c>
       <c r="F8">
-        <v>72.09</v>
+        <v>72.08984375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2438,13 +2438,13 @@
         <v>36</v>
       </c>
       <c r="D9">
-        <v>47.39</v>
+        <v>47.389892578125</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
       </c>
       <c r="F9">
-        <v>54.81</v>
+        <v>54.81005859375</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2458,13 +2458,13 @@
         <v>39</v>
       </c>
       <c r="D10">
-        <v>65.89</v>
+        <v>65.89013671875</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10">
-        <v>73.22</v>
+        <v>73.22021484375</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2478,13 +2478,13 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>53.46</v>
+        <v>53.4599609375</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11">
-        <v>62.81</v>
+        <v>62.81005859375</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2498,13 +2498,13 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>66.51000000000001</v>
+        <v>66.509765625</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>67.19</v>
+        <v>67.18994140625</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2518,13 +2518,13 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>58.61</v>
+        <v>58.610107421875</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
       <c r="F13">
-        <v>54.62</v>
+        <v>54.6201171875</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2538,13 +2538,13 @@
         <v>43</v>
       </c>
       <c r="D14">
-        <v>62.1</v>
+        <v>62.10009765625</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
       </c>
       <c r="F14">
-        <v>69.42</v>
+        <v>69.419921875</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2558,13 +2558,13 @@
         <v>42</v>
       </c>
       <c r="D15">
-        <v>69.12</v>
+        <v>69.1201171875</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
       </c>
       <c r="F15">
-        <v>56.11</v>
+        <v>56.110107421875</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2578,7 +2578,7 @@
         <v>45</v>
       </c>
       <c r="D16">
-        <v>77.41</v>
+        <v>77.41015625</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -2598,13 +2598,13 @@
         <v>44</v>
       </c>
       <c r="D17">
-        <v>52.2</v>
+        <v>52.199951171875</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
       </c>
       <c r="F17">
-        <v>65.70999999999999</v>
+        <v>65.7099609375</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -2297,15 +2297,9 @@
       <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="D2">
-        <v>62.919921875</v>
-      </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2">
-        <v>54.2099609375</v>
-      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -2317,14 +2311,8 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="D3">
-        <v>62.010009765625</v>
-      </c>
       <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="F3">
-        <v>48.199951171875</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2337,14 +2325,8 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="D4">
-        <v>72.10986328125</v>
-      </c>
       <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="F4">
-        <v>64.35986328125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2357,14 +2339,8 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5">
-        <v>64.1201171875</v>
-      </c>
       <c r="E5" t="s">
         <v>16</v>
-      </c>
-      <c r="F5">
-        <v>44.510009765625</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2377,14 +2353,8 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="D6">
-        <v>83</v>
-      </c>
       <c r="E6" t="s">
         <v>19</v>
-      </c>
-      <c r="F6">
-        <v>86.419921875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2397,14 +2367,8 @@
       <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7">
-        <v>66.60986328125</v>
-      </c>
       <c r="E7" t="s">
         <v>18</v>
-      </c>
-      <c r="F7">
-        <v>56.39990234375</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2417,14 +2381,8 @@
       <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8">
-        <v>68.7998046875</v>
-      </c>
       <c r="E8" t="s">
         <v>21</v>
-      </c>
-      <c r="F8">
-        <v>72.08984375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2437,14 +2395,8 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9">
-        <v>47.389892578125</v>
-      </c>
       <c r="E9" t="s">
         <v>20</v>
-      </c>
-      <c r="F9">
-        <v>54.81005859375</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2457,14 +2409,8 @@
       <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="D10">
-        <v>65.89013671875</v>
-      </c>
       <c r="E10" t="s">
         <v>23</v>
-      </c>
-      <c r="F10">
-        <v>73.22021484375</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2477,14 +2423,8 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="D11">
-        <v>53.4599609375</v>
-      </c>
       <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="F11">
-        <v>62.81005859375</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2497,14 +2437,8 @@
       <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="D12">
-        <v>66.509765625</v>
-      </c>
       <c r="E12" t="s">
         <v>25</v>
-      </c>
-      <c r="F12">
-        <v>67.18994140625</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2517,14 +2451,8 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13">
-        <v>58.610107421875</v>
-      </c>
       <c r="E13" t="s">
         <v>24</v>
-      </c>
-      <c r="F13">
-        <v>54.6201171875</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2537,14 +2465,8 @@
       <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="D14">
-        <v>62.10009765625</v>
-      </c>
       <c r="E14" t="s">
         <v>27</v>
-      </c>
-      <c r="F14">
-        <v>69.419921875</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2557,14 +2479,8 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="D15">
-        <v>69.1201171875</v>
-      </c>
       <c r="E15" t="s">
         <v>26</v>
-      </c>
-      <c r="F15">
-        <v>56.110107421875</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2577,17 +2493,11 @@
       <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="D16">
-        <v>77.41015625</v>
-      </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
-      <c r="F16">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2597,14 +2507,8 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
-      <c r="D17">
-        <v>52.199951171875</v>
-      </c>
       <c r="E17" t="s">
         <v>28</v>
-      </c>
-      <c r="F17">
-        <v>65.7099609375</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_1.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_1.xlsx
@@ -2297,9 +2297,15 @@
       <c r="C2" t="s">
         <v>31</v>
       </c>
+      <c r="D2">
+        <v>62.919921875</v>
+      </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2">
+        <v>54.2099609375</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -2311,8 +2317,14 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
+      <c r="D3">
+        <v>62.010009765625</v>
+      </c>
       <c r="E3" t="s">
         <v>14</v>
+      </c>
+      <c r="F3">
+        <v>48.199951171875</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2325,8 +2337,14 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
+      <c r="D4">
+        <v>72.10986328125</v>
+      </c>
       <c r="E4" t="s">
         <v>17</v>
+      </c>
+      <c r="F4">
+        <v>64.35986328125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2339,8 +2357,14 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
+      <c r="D5">
+        <v>64.1201171875</v>
+      </c>
       <c r="E5" t="s">
         <v>16</v>
+      </c>
+      <c r="F5">
+        <v>44.510009765625</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2353,8 +2377,14 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
+      <c r="D6">
+        <v>83</v>
+      </c>
       <c r="E6" t="s">
         <v>19</v>
+      </c>
+      <c r="F6">
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2367,8 +2397,14 @@
       <c r="C7" t="s">
         <v>34</v>
       </c>
+      <c r="D7">
+        <v>66.60986328125</v>
+      </c>
       <c r="E7" t="s">
         <v>18</v>
+      </c>
+      <c r="F7">
+        <v>56.39990234375</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2381,8 +2417,14 @@
       <c r="C8" t="s">
         <v>37</v>
       </c>
+      <c r="D8">
+        <v>68.7998046875</v>
+      </c>
       <c r="E8" t="s">
         <v>21</v>
+      </c>
+      <c r="F8">
+        <v>72.08984375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2395,8 +2437,14 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
+      <c r="D9">
+        <v>47.389892578125</v>
+      </c>
       <c r="E9" t="s">
         <v>20</v>
+      </c>
+      <c r="F9">
+        <v>54.81005859375</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2409,8 +2457,14 @@
       <c r="C10" t="s">
         <v>39</v>
       </c>
+      <c r="D10">
+        <v>65.89013671875</v>
+      </c>
       <c r="E10" t="s">
         <v>23</v>
+      </c>
+      <c r="F10">
+        <v>73.22021484375</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2423,8 +2477,14 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
+      <c r="D11">
+        <v>53.4599609375</v>
+      </c>
       <c r="E11" t="s">
         <v>22</v>
+      </c>
+      <c r="F11">
+        <v>62.81005859375</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2437,8 +2497,14 @@
       <c r="C12" t="s">
         <v>41</v>
       </c>
+      <c r="D12">
+        <v>66.509765625</v>
+      </c>
       <c r="E12" t="s">
         <v>25</v>
+      </c>
+      <c r="F12">
+        <v>67.18994140625</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2451,8 +2517,14 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
+      <c r="D13">
+        <v>58.610107421875</v>
+      </c>
       <c r="E13" t="s">
         <v>24</v>
+      </c>
+      <c r="F13">
+        <v>54.6201171875</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2465,8 +2537,14 @@
       <c r="C14" t="s">
         <v>43</v>
       </c>
+      <c r="D14">
+        <v>62.10009765625</v>
+      </c>
       <c r="E14" t="s">
         <v>27</v>
+      </c>
+      <c r="F14">
+        <v>69.419921875</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2479,8 +2557,14 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
+      <c r="D15">
+        <v>69.1201171875</v>
+      </c>
       <c r="E15" t="s">
         <v>26</v>
+      </c>
+      <c r="F15">
+        <v>56.110107421875</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2493,11 +2577,17 @@
       <c r="C16" t="s">
         <v>45</v>
       </c>
+      <c r="D16">
+        <v>77.41015625</v>
+      </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2507,8 +2597,14 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
+      <c r="D17">
+        <v>52.199951171875</v>
+      </c>
       <c r="E17" t="s">
         <v>28</v>
+      </c>
+      <c r="F17">
+        <v>65.7099609375</v>
       </c>
     </row>
   </sheetData>
